--- a/敏捷开发Sprint追踪表.xlsx
+++ b/敏捷开发Sprint追踪表.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\教学\PBL-AI_驱动软件工程实践\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E85D9C0-C30B-4218-ABD3-BC7FAD54183D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="需求列表" sheetId="5" r:id="rId1"/>
@@ -19,23 +13,147 @@
     <sheet name="SprintN迭代计划 " sheetId="6" r:id="rId4"/>
     <sheet name="迭代回顾" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+  <si>
+    <t>模块</t>
+  </si>
+  <si>
+    <t>功能需求</t>
+  </si>
+  <si>
+    <t>需求描述</t>
+  </si>
+  <si>
+    <t>用户管理</t>
+  </si>
+  <si>
+    <t>用户注册</t>
+  </si>
+  <si>
+    <t>登录</t>
+  </si>
+  <si>
+    <t>个人信息管理</t>
+  </si>
+  <si>
+    <t>活动管理</t>
+  </si>
+  <si>
+    <t>发布活动、编辑活动、删除活动。</t>
+  </si>
+  <si>
+    <t>活动报名</t>
+  </si>
+  <si>
+    <t>用户报名活动、查看报名信息。</t>
+  </si>
+  <si>
+    <t>评论互动</t>
+  </si>
+  <si>
+    <t>用户评论活动。</t>
+  </si>
+  <si>
+    <t>收藏</t>
+  </si>
+  <si>
+    <t>收藏感兴趣的活动。</t>
+  </si>
+  <si>
+    <t>用户故事</t>
+  </si>
+  <si>
+    <t>优先级(P0-P5)</t>
+  </si>
+  <si>
+    <t>工作量(小时)</t>
+  </si>
   <si>
     <t>迭代周期</t>
   </si>
   <si>
-    <t>用户故事</t>
+    <t>状态(TODO/On going/Done)</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>作为一个用户，我需要注册新用户从而使用这个系统</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>Sprint1 (2016/03/24~2026/04/7)</t>
+  </si>
+  <si>
+    <t>任务</t>
+  </si>
+  <si>
+    <t>工作量</t>
   </si>
   <si>
     <t>负责人</t>
   </si>
   <si>
-    <t>备注</t>
+    <t>Sprint1</t>
+  </si>
+  <si>
+    <t>用户注册开发</t>
+  </si>
+  <si>
+    <t>张三</t>
+  </si>
+  <si>
+    <t>用户注册测试</t>
+  </si>
+  <si>
+    <t>李四</t>
+  </si>
+  <si>
+    <t>Sprint1 (2016/0x/xx~2026/0x/xx)</t>
+  </si>
+  <si>
+    <t>用户登录</t>
+  </si>
+  <si>
+    <t>登录功能开发</t>
+  </si>
+  <si>
+    <t>朱桔满</t>
+  </si>
+  <si>
+    <t>登录功能测试</t>
+  </si>
+  <si>
+    <t>孙睿龙</t>
+  </si>
+  <si>
+    <t>注册功能开发</t>
+  </si>
+  <si>
+    <t>吕林坤</t>
+  </si>
+  <si>
+    <t>注册功能测试</t>
   </si>
   <si>
     <t>做得好的</t>
@@ -47,203 +165,209 @@
     <t>行动项</t>
   </si>
   <si>
-    <t>需求描述</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>功能需求</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>模块</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户管理</t>
-  </si>
-  <si>
-    <t>发布活动、编辑活动、删除活动。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>活动管理</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>活动报名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>评论互动</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>收藏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户报名活动、查看报名信息。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户评论活动。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>收藏感兴趣的活动。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户注册</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>登录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>个人信息管理</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户故事</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>任务</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>作为一个用户，我需要注册新用户从而使用这个系统</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>P0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>优先级(P0-P5)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作量</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作量(小时)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprint1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Sprint 1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Sprint 2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>状态(TODO/On going/Done)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户注册开发</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户注册测试</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>张三</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>李四</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprint1 (2016/03/24~2026/04/7)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户退出登录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>退出登录开发</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>退出登录测试</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprint1 (2016/0x/xx~2026/0x/xx)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <color theme="0"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="黑体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -252,18 +376,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.249977111117893"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -271,81 +581,346 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D6422DF1-4911-4D96-B219-EF9E6F1557B1}" name="表2" displayName="表2" ref="A1:F22" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:F22" xr:uid="{D6422DF1-4911-4D96-B219-EF9E6F1557B1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表2" displayName="表2" ref="A1:F22" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F22" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{738C9201-C776-4B34-9C9C-9A47E5896D7A}" name="用户故事"/>
-    <tableColumn id="4" xr3:uid="{32DA33D9-AB43-4E64-B1B8-A26FEDCAEED5}" name="优先级(P0-P5)"/>
-    <tableColumn id="5" xr3:uid="{981B1E69-33B1-48F8-8F20-29035D16874F}" name="工作量(小时)"/>
-    <tableColumn id="1" xr3:uid="{F6735E89-0EA2-4ADF-8E1A-55B368656517}" name="迭代周期"/>
-    <tableColumn id="7" xr3:uid="{05625A87-C49D-4ED2-BBED-0CA3906DFCB2}" name="状态(TODO/On going/Done)"/>
-    <tableColumn id="6" xr3:uid="{AC06270F-3F1E-406A-B15B-04E99A36786C}" name="备注"/>
+    <tableColumn id="2" name="用户故事"/>
+    <tableColumn id="4" name="优先级(P0-P5)"/>
+    <tableColumn id="5" name="工作量(小时)"/>
+    <tableColumn id="1" name="迭代周期"/>
+    <tableColumn id="7" name="状态(TODO/On going/Done)"/>
+    <tableColumn id="6" name="备注"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -630,138 +1205,139 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DB11394-F6C9-4967-9952-94DD70A7E791}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="23.06640625" customWidth="1"/>
-    <col min="3" max="3" width="41.86328125" customWidth="1"/>
+    <col min="2" max="2" width="23.0648148148148" customWidth="1"/>
+    <col min="3" max="3" width="41.8611111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B8" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:A4"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="59.53125" customWidth="1"/>
+    <col min="1" max="1" width="59.5277777777778" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="23.86328125" customWidth="1"/>
+    <col min="3" max="3" width="23.8611111111111" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="28.9296875" customWidth="1"/>
+    <col min="5" max="5" width="28.9259259259259" customWidth="1"/>
     <col min="6" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>24</v>
+    <row r="1" spans="1:6">
+      <c r="A1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -769,218 +1345,246 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="3" width="26.73046875" customWidth="1"/>
+    <col min="2" max="3" width="26.7314814814815" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="26.796875" customWidth="1"/>
+    <col min="6" max="6" width="26.7962962962963" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B1" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="4" t="s">
+    <row r="1" spans="1:7">
+      <c r="B1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="C4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:G1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC9F5045-2C5D-4607-A2B6-8C509A9AF321}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="24.1328125" customWidth="1"/>
+    <col min="4" max="4" width="24.1296296296296" customWidth="1"/>
     <col min="5" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="4" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3">
         <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3">
-        <v>8</v>
       </c>
       <c r="D3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" t="s">
         <v>40</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>36</v>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A8"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/敏捷开发Sprint追踪表.xlsx
+++ b/敏捷开发Sprint追踪表.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>模块</t>
   </si>
@@ -154,6 +154,18 @@
   </si>
   <si>
     <t>注册功能测试</t>
+  </si>
+  <si>
+    <t>用户登录优化</t>
+  </si>
+  <si>
+    <t>登录优化</t>
+  </si>
+  <si>
+    <t>学生使用学号可以直接登录不用注册</t>
+  </si>
+  <si>
+    <t>登陆功能测试</t>
   </si>
   <si>
     <t>做得好的</t>
@@ -181,7 +193,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,13 +228,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -367,7 +372,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,12 +430,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,148 +681,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1431,8 +1430,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="24.1296296296296" customWidth="1"/>
@@ -1516,6 +1515,34 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1542,13 +1569,13 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -1556,7 +1583,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1567,7 +1594,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:5">

--- a/敏捷开发Sprint追踪表.xlsx
+++ b/敏捷开发Sprint追踪表.xlsx
@@ -1526,7 +1526,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
         <v>35</v>

--- a/敏捷开发Sprint追踪表.xlsx
+++ b/敏捷开发Sprint追踪表.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
   <si>
     <t>模块</t>
   </si>
@@ -166,6 +166,70 @@
   </si>
   <si>
     <t>登陆功能测试</t>
+  </si>
+  <si>
+    <t>前端页面初步搭建</t>
+  </si>
+  <si>
+    <t>前端页面搭建</t>
+  </si>
+  <si>
+    <t>使用mock数据进行模拟后期更换为后端</t>
+  </si>
+  <si>
+    <t>前端页面功能审核</t>
+  </si>
+  <si>
+    <t>后端功能初步实现</t>
+  </si>
+  <si>
+    <t>按前端功能进行分析并对数据库进行修改</t>
+  </si>
+  <si>
+    <t>朱桔满，吕林坤</t>
+  </si>
+  <si>
+    <t>后端模块开发</t>
+  </si>
+  <si>
+    <t>三端登录判断，活动获取模块，报名模块，活动发布模块等</t>
+  </si>
+  <si>
+    <t>项目初步测试</t>
+  </si>
+  <si>
+    <t>测试项目现有功能</t>
+  </si>
+  <si>
+    <t>活动展示模块不显示活动，活动详情页不显示。发布者端功能模块不跳转</t>
+  </si>
+  <si>
+    <t>项目bug修复</t>
+  </si>
+  <si>
+    <t>bug修复</t>
+  </si>
+  <si>
+    <t>bug修复后再测试</t>
+  </si>
+  <si>
+    <t>测试是否修复成功</t>
+  </si>
+  <si>
+    <t>活动详情页统计人数显示错误为0，详情页报名功能取消报名后无法再次报名。缺少活动主办方选项。并且无法发布活动</t>
+  </si>
+  <si>
+    <t>bug	修复</t>
+  </si>
+  <si>
+    <t>活动发布者端发布页面缺少活动主办方的选项，导致提交审核出现报错，
+因为数据库里 organizer 字段不允许为 null。修复方案为发布者端添加上活动主办方选项</t>
+  </si>
+  <si>
+    <t>功能添加</t>
+  </si>
+  <si>
+    <t>活动发布时添加加分选项，限制身份报名活动</t>
   </si>
   <si>
     <t>做得好的</t>
@@ -826,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -834,11 +898,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1218,13 +1294,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1232,19 +1308,19 @@
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2"/>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2"/>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1252,7 +1328,7 @@
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1260,7 +1336,7 @@
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1268,7 +1344,7 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1276,7 +1352,7 @@
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1304,27 +1380,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
@@ -1358,14 +1434,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
@@ -1430,125 +1506,268 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="24.1296296296296" customWidth="1"/>
-    <col min="5" max="7" width="22" customWidth="1"/>
+    <col min="1" max="3" width="22" style="3" customWidth="1"/>
+    <col min="4" max="4" width="24.1296296296296" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22" style="3" customWidth="1"/>
+    <col min="6" max="6" width="26.8888888888889" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="B4" t="s">
+    <row r="4" spans="1:7">
+      <c r="B4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>2</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="B6" t="s">
+    <row r="6" spans="1:7">
+      <c r="B6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="3">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+    <row r="7" spans="1:7">
+      <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="B8" t="s">
+    <row r="8" spans="1:7">
+      <c r="B8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>37</v>
       </c>
     </row>
+    <row r="9" ht="28.8" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" ht="28.8" spans="1:7">
+      <c r="A11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" ht="43.2" spans="1:7">
+      <c r="B12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="3">
+        <v>4</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="8"/>
+    </row>
+    <row r="13" ht="43.2" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" ht="72" spans="1:6">
+      <c r="A18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="3">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" ht="100.8" spans="1:6">
+      <c r="A20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="3">
+        <v>4</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" ht="28.8" spans="1:6">
+      <c r="A22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1569,13 +1788,13 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -1583,7 +1802,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1594,7 +1813,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:5">
